--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92069</v>
+        <v>92071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92071</v>
+        <v>92085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135891017</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135890827</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135890884</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135890911</v>
       </c>
       <c r="B10" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>135891351</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135891066</v>
       </c>
       <c r="B12" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135891196</v>
       </c>
       <c r="B13" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135891212</v>
       </c>
       <c r="B14" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92085</v>
+        <v>92086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92086</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135891017</v>
       </c>
       <c r="B7" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135890827</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135890884</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135890911</v>
       </c>
       <c r="B10" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>135891351</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135891066</v>
       </c>
       <c r="B12" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135891196</v>
       </c>
       <c r="B13" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135891212</v>
       </c>
       <c r="B14" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135891017</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135890827</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135890884</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135890911</v>
       </c>
       <c r="B10" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>135891351</v>
       </c>
       <c r="B11" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135891066</v>
       </c>
       <c r="B12" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135891196</v>
       </c>
       <c r="B13" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135891212</v>
       </c>
       <c r="B14" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92094</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135891017</v>
       </c>
       <c r="B7" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135890827</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135890884</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135890911</v>
       </c>
       <c r="B10" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>135891351</v>
       </c>
       <c r="B11" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135891066</v>
       </c>
       <c r="B12" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135891196</v>
       </c>
       <c r="B13" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135891212</v>
       </c>
       <c r="B14" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135891017</v>
       </c>
       <c r="B7" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135890827</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135890884</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135890911</v>
       </c>
       <c r="B10" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>135891351</v>
       </c>
       <c r="B11" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135891066</v>
       </c>
       <c r="B12" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135891196</v>
       </c>
       <c r="B13" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135891212</v>
       </c>
       <c r="B14" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1252,7 +1252,7 @@
         <v>135891017</v>
       </c>
       <c r="B7" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>135890827</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>135890884</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1613,7 +1613,7 @@
         <v>135890911</v>
       </c>
       <c r="B10" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>135891351</v>
       </c>
       <c r="B11" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>135891066</v>
       </c>
       <c r="B12" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1964,7 +1964,7 @@
         <v>135891196</v>
       </c>
       <c r="B13" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2081,7 +2081,7 @@
         <v>135891212</v>
       </c>
       <c r="B14" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 23828-2026 artfynd.xlsx
+++ b/artfynd/A 23828-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135891144</v>
       </c>
       <c r="B2" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>135890842</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -916,7 +916,7 @@
         <v>135890929</v>
       </c>
       <c r="B4" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>135891118</v>
       </c>
       <c r="B5" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>135891289</v>
       </c>
       <c r="B6" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
